--- a/03_設計書/画面遷移図.xlsx
+++ b/03_設計書/画面遷移図.xlsx
@@ -5,20 +5,20 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HDC242310\Documents\卒業研究\設計書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\sotsuken242310\03_設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834951B4-D743-4F06-B959-645AF4110851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C058E1-0A36-4B5C-AAA5-70C5C8883DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4632" yWindow="1440" windowWidth="17172" windowHeight="10308" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="13965" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
-    <sheet name="入出金管理" sheetId="1" r:id="rId2"/>
+    <sheet name="tbatter" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">入出金管理!$A$1:$Q$50</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">入出金管理!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">tbatter!$A$1:$Q$50</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">tbatter!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
   <extLst>
@@ -870,44 +870,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -953,8 +915,46 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -1015,8 +1015,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1463040" y="784860"/>
-          <a:ext cx="6591300" cy="228600"/>
+          <a:off x="1600200" y="807720"/>
+          <a:ext cx="7208520" cy="232410"/>
           <a:chOff x="1234" y="3654"/>
           <a:chExt cx="9721" cy="360"/>
         </a:xfrm>
@@ -1169,8 +1169,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1463040" y="2872740"/>
-          <a:ext cx="6591300" cy="220980"/>
+          <a:off x="1600200" y="2956560"/>
+          <a:ext cx="7208520" cy="224790"/>
           <a:chOff x="1234" y="5634"/>
           <a:chExt cx="9721" cy="360"/>
         </a:xfrm>
@@ -1534,16 +1534,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>769063</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>18683</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>491753</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>139253</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>6725</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>112900</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>127295</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>88786</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1558,8 +1558,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2746405" y="2227518"/>
-          <a:ext cx="1031738" cy="634369"/>
+          <a:off x="5266310" y="1284664"/>
+          <a:ext cx="1239118" cy="672951"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1623,16 +1623,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>769063</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>22705</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>491753</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>143275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>6725</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>131563</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>127295</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>107449</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1647,8 +1647,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2746405" y="3176806"/>
-          <a:ext cx="1031738" cy="649010"/>
+          <a:off x="5266310" y="2301471"/>
+          <a:ext cx="1239118" cy="687592"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1697,16 +1697,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>392885</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>41368</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>43234</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>29310</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>547</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>48229</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>133173</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1721,8 +1721,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2370227" y="4140735"/>
-          <a:ext cx="1401191" cy="634369"/>
+          <a:off x="5336240" y="3344975"/>
+          <a:ext cx="1608571" cy="682597"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2026,14 +2026,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1597805</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>28682</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>113081</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>511215</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>3069</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>87468</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2048,8 +2048,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1858235" y="5478429"/>
-          <a:ext cx="1479132" cy="649577"/>
+          <a:off x="1887172" y="6467100"/>
+          <a:ext cx="1770910" cy="697805"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2115,15 +2115,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1434353</xdr:colOff>
+      <xdr:colOff>1458891</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>65258</xdr:rowOff>
+      <xdr:rowOff>60285</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1597805</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>83395</xdr:rowOff>
+      <xdr:colOff>1597804</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>27933</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2140,8 +2140,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000" flipH="1">
-          <a:off x="-325648" y="3619335"/>
-          <a:ext cx="4204314" cy="163452"/>
+          <a:off x="-770413" y="4158418"/>
+          <a:ext cx="5176256" cy="138913"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector2">
           <a:avLst/>
@@ -2173,15 +2173,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>257846</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>29933</xdr:rowOff>
+      <xdr:colOff>257845</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>114332</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>231492</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>3753</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>96454</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>88152</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2196,8 +2196,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3682023" y="5479680"/>
-          <a:ext cx="1304735" cy="649010"/>
+          <a:off x="4067845" y="6468351"/>
+          <a:ext cx="1888293" cy="697238"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2256,10 +2256,16 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>検索・凍結・削除</a:t>
+            <a:t>検索・凍結・削除・作成</a:t>
           </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
             <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2270,14 +2276,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>499165</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>84362</xdr:rowOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>24077</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>257846</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>84362</xdr:rowOff>
+      <xdr:colOff>257845</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>28900</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2294,8 +2300,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3325317" y="5804185"/>
-          <a:ext cx="356706" cy="0"/>
+          <a:off x="3646032" y="6812147"/>
+          <a:ext cx="421813" cy="4823"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2327,16 +2333,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>436122</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>108878</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>173621</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>41678</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>437582</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>18683</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>491753</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>54449</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2348,14 +2354,14 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="2"/>
-          <a:endCxn id="6" idx="0"/>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="6" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="3262274" y="1912600"/>
-          <a:ext cx="1460" cy="314918"/>
+        <a:xfrm flipV="1">
+          <a:off x="4610583" y="1621140"/>
+          <a:ext cx="655727" cy="12771"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2387,41 +2393,112 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>443842</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>116596</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>7063</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>10019</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>443842</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>26400</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>12058</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>113881</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="テキスト ボックス 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DD358FD-38DA-4ECF-A34D-9D9419835C25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5300069" y="4338468"/>
+          <a:ext cx="1608571" cy="682597"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="19050" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>メッセージ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>116228</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>55945</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>7062</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>61951</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="61" name="直線矢印コネクタ 60">
+        <xdr:cNvPr id="26" name="カギ線コネクタ 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EB86646-B16E-453F-A01F-9CDE8711B888}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{038B2A37-FCB0-4A68-B6DE-5722B86C12DC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="21" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3269994" y="2865583"/>
-          <a:ext cx="0" cy="314918"/>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="3573247" y="2952945"/>
+          <a:ext cx="3044360" cy="409283"/>
         </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
+        <a:prstGeom prst="bentConnector2">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="tx1"/>
           </a:solidFill>
-          <a:headEnd type="arrow"/>
           <a:tailEnd type="arrow"/>
         </a:ln>
       </xdr:spPr>
@@ -2444,41 +2521,100 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>451559</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>133956</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123946</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>51604</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>451559</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>43760</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>43234</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>81241</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="62" name="直線矢印コネクタ 61">
+        <xdr:cNvPr id="28" name="カギ線コネクタ 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD60B190-C880-474A-B196-AFF53F5C68EB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAFDE020-B078-4EC8-8CC5-9AA739C8DB34}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="8" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3277711" y="3828209"/>
-          <a:ext cx="0" cy="314918"/>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="4089768" y="2439801"/>
+          <a:ext cx="2055207" cy="437737"/>
         </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
+        <a:prstGeom prst="bentConnector2">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="tx1"/>
           </a:solidFill>
-          <a:headEnd type="arrow"/>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>119606</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>59319</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>491754</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>53019</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="カギ線コネクタ 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63511328-D585-4AEE-8CBF-5DBE42B9D353}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="7" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="4576994" y="1955950"/>
+          <a:ext cx="1006485" cy="372148"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
           <a:tailEnd type="arrow"/>
         </a:ln>
       </xdr:spPr>
@@ -2824,9 +2960,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AZ52"/>
-  <sheetFormatPr defaultColWidth="2.6640625" defaultRowHeight="9.6" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="2.625" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="2.6640625" style="32"/>
+    <col min="1" max="16384" width="2.625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -5683,68 +5819,68 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet58"/>
   <dimension ref="A1:Q84"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="10.8" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="3.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="4.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" style="1" customWidth="1"/>
-    <col min="10" max="12" width="6.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="6.21875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="12.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="6.33203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="14.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5" style="1" customWidth="1"/>
+    <col min="10" max="12" width="6.875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="6.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5" style="1" customWidth="1"/>
+    <col min="15" max="15" width="6.375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14.375" style="1" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="68" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="57" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="61"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="77"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="64"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="71" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="54" t="s">
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="56"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="72"/>
       <c r="M2" s="17" t="s">
         <v>0</v>
       </c>
@@ -5762,22 +5898,22 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="64"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="74" t="s">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="48" t="s">
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="50"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="68"/>
       <c r="M3" s="21" t="s">
         <v>2</v>
       </c>
@@ -5789,22 +5925,22 @@
       <c r="Q3" s="24"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="51" t="s">
+      <c r="A4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="51" t="s">
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="53"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="69"/>
       <c r="M4" s="25" t="s">
         <v>4</v>
       </c>
@@ -5815,7 +5951,7 @@
       <c r="P4" s="27"/>
       <c r="Q4" s="28"/>
     </row>
-    <row r="5" spans="1:17" ht="7.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="7.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -6670,7 +6806,7 @@
       <c r="P49" s="4"/>
       <c r="Q49" s="13"/>
     </row>
-    <row r="50" spans="1:17" ht="11.4" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17" ht="12" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A50" s="14"/>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -6997,16 +7133,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="H4:L4"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="M1:Q1"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="D4:G4"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="H4:L4"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="H1:L1"/>
-    <mergeCell ref="M1:Q1"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.27559055118110237" right="0.27559055118110237" top="0.47244094488188981" bottom="0.47244094488188981" header="0.27559055118110237" footer="0.27559055118110237"/>
